--- a/research/traditional_assets/database/data/jordan/jordan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0243</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="E2">
-        <v>0.07024999999999999</v>
+        <v>-0.2191</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7.254</v>
+        <v>5.053999999999999</v>
       </c>
       <c r="L2">
-        <v>0.4542835671342685</v>
+        <v>0.4714552238805969</v>
       </c>
       <c r="M2">
-        <v>0.233</v>
+        <v>2.82</v>
       </c>
       <c r="N2">
-        <v>0.003322875071306332</v>
+        <v>0.02881078872088271</v>
       </c>
       <c r="O2">
-        <v>0.03212020953956438</v>
+        <v>0.5579738820736051</v>
       </c>
       <c r="P2">
-        <v>0.233</v>
+        <v>2.82</v>
       </c>
       <c r="Q2">
-        <v>0.003322875071306332</v>
+        <v>0.02881078872088271</v>
       </c>
       <c r="R2">
-        <v>0.03212020953956438</v>
+        <v>0.5579738820736051</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.181</v>
+        <v>3.397</v>
       </c>
       <c r="V2">
-        <v>0.08814888762122076</v>
+        <v>0.03470576215774417</v>
       </c>
       <c r="W2">
-        <v>0.06344936708860759</v>
+        <v>0.0008904109589041096</v>
       </c>
       <c r="X2">
-        <v>0.03216093617811172</v>
+        <v>0.06636722681768881</v>
       </c>
       <c r="Y2">
-        <v>0.03128843091049587</v>
+        <v>-0.0654768158587847</v>
       </c>
       <c r="Z2">
-        <v>0.1118881118881119</v>
+        <v>0.04562517556329216</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03278186352929871</v>
+        <v>0.07068494522063501</v>
       </c>
       <c r="AC2">
-        <v>-0.03278186352929871</v>
+        <v>-0.07068494522063501</v>
       </c>
       <c r="AD2">
-        <v>51.14</v>
+        <v>91.87299999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.14</v>
+        <v>91.87299999999999</v>
       </c>
       <c r="AG2">
-        <v>44.959</v>
+        <v>88.47599999999998</v>
       </c>
       <c r="AH2">
-        <v>0.421738413326736</v>
+        <v>0.4841715282498827</v>
       </c>
       <c r="AI2">
-        <v>0.2948570110701107</v>
+        <v>0.3988010747787284</v>
       </c>
       <c r="AJ2">
-        <v>0.3906794462934158</v>
+        <v>0.4747687222305694</v>
       </c>
       <c r="AK2">
-        <v>0.2687986894576674</v>
+        <v>0.3898033272240236</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="AQ2">
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -709,26 +712,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0304</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>-0.056</v>
-      </c>
-      <c r="L3">
-        <v>-0.06526806526806526</v>
+        <v>-0.283</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,31 +737,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.251</v>
+        <v>0.503</v>
       </c>
       <c r="V3">
-        <v>0.03971518987341772</v>
+        <v>0.09710424710424712</v>
       </c>
       <c r="W3">
-        <v>-0.003916083916083916</v>
+        <v>-0.01979020979020979</v>
       </c>
       <c r="X3">
-        <v>0.0316634351652073</v>
+        <v>0.0603979423920712</v>
       </c>
       <c r="Y3">
-        <v>-0.03557951908129121</v>
+        <v>-0.08018815218228099</v>
       </c>
       <c r="Z3">
-        <v>0.06457439602619101</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0316634351652073</v>
+        <v>0.0603979423920712</v>
       </c>
       <c r="AC3">
-        <v>-0.0316634351652073</v>
+        <v>-0.0603979423920712</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.251</v>
+        <v>-0.503</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0413577195584116</v>
+        <v>-0.1075475732307034</v>
       </c>
       <c r="AK3">
-        <v>-0.01786604028756495</v>
+        <v>-0.0372675409350226</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,10 +811,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0243</v>
+        <v>-0.227</v>
       </c>
       <c r="E4">
-        <v>-0.0395</v>
+        <v>-0.519</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,85 +829,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>4.01</v>
+        <v>0.117</v>
       </c>
       <c r="L4">
-        <v>0.6140888208269525</v>
+        <v>0.05467289719626169</v>
       </c>
       <c r="M4">
-        <v>0.227</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.008194945848375452</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.05660847880299252</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.227</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.008194945848375452</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.05660847880299252</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>0.09205776173285198</v>
+        <v>0.06538461538461539</v>
       </c>
       <c r="W4">
-        <v>0.06344936708860759</v>
+        <v>0.001780821917808219</v>
       </c>
       <c r="X4">
-        <v>0.03216093617811172</v>
+        <v>0.0609676447606229</v>
       </c>
       <c r="Y4">
-        <v>0.03128843091049587</v>
+        <v>-0.05918682284281468</v>
       </c>
       <c r="Z4">
-        <v>0.1042797828169914</v>
+        <v>0.03333852625019473</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03278186352929871</v>
+        <v>0.06192953872454171</v>
       </c>
       <c r="AC4">
-        <v>-0.03278186352929871</v>
+        <v>-0.06192953872454171</v>
       </c>
       <c r="AD4">
-        <v>1.04</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.04</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AG4">
-        <v>-1.51</v>
+        <v>-0.9270000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.03618649965205289</v>
+        <v>0.03191957485698811</v>
       </c>
       <c r="AI4">
-        <v>0.01558285885525921</v>
+        <v>0.01443153819077789</v>
       </c>
       <c r="AJ4">
-        <v>-0.05765559373806796</v>
+        <v>-0.03349835579807033</v>
       </c>
       <c r="AK4">
-        <v>-0.02352391338214675</v>
+        <v>-0.01460463504167126</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -939,7 +921,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bindar Trading and Investment Company (ASE:BIND)</t>
+          <t>Future Arab Investment Company (ASE:FUTR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,110 +929,205 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.167</v>
-      </c>
-      <c r="E5">
-        <v>0.18</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
-        <v>3.3</v>
-      </c>
-      <c r="L5">
-        <v>0.3846153846153846</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.006</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.0001662049861495845</v>
-      </c>
-      <c r="O5">
-        <v>0.001818181818181818</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.006</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0001662049861495845</v>
-      </c>
-      <c r="R5">
-        <v>0.001818181818181818</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>3.38</v>
+        <v>0.75</v>
       </c>
       <c r="V5">
-        <v>0.09362880886426592</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="W5">
-        <v>0.08461538461538461</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>0.05005297758685574</v>
+        <v>0.07176680887475473</v>
       </c>
       <c r="Y5">
-        <v>0.03456240702852887</v>
+        <v>-0.07176680887475473</v>
       </c>
       <c r="Z5">
-        <v>0.1284296555750146</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05319072745202083</v>
+        <v>0.07944035171672829</v>
       </c>
       <c r="AC5">
-        <v>-0.05319072745202083</v>
+        <v>-0.07944035171672829</v>
       </c>
       <c r="AD5">
-        <v>50.1</v>
+        <v>7.83</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>50.1</v>
+        <v>7.83</v>
       </c>
       <c r="AG5">
-        <v>46.72</v>
+        <v>7.08</v>
       </c>
       <c r="AH5">
-        <v>0.5812064965197216</v>
+        <v>0.3968575772934617</v>
       </c>
       <c r="AI5">
-        <v>0.5422077922077921</v>
+        <v>0.2155243600330306</v>
       </c>
       <c r="AJ5">
-        <v>0.5641149480801739</v>
+        <v>0.3730242360379347</v>
       </c>
       <c r="AK5">
-        <v>0.5248258818243091</v>
+        <v>0.1989881956155143</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Comprehensive Leasing Company (ASE:LEAS)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.06860000000000001</v>
+      </c>
+      <c r="E6">
+        <v>0.0808</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>5.22</v>
+      </c>
+      <c r="L6">
+        <v>0.6083916083916083</v>
+      </c>
+      <c r="M6">
+        <v>2.82</v>
+      </c>
+      <c r="N6">
+        <v>0.05402298850574712</v>
+      </c>
+      <c r="O6">
+        <v>0.5402298850574713</v>
+      </c>
+      <c r="P6">
+        <v>2.82</v>
+      </c>
+      <c r="Q6">
+        <v>0.05402298850574712</v>
+      </c>
+      <c r="R6">
+        <v>0.5402298850574713</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.274</v>
+      </c>
+      <c r="V6">
+        <v>0.00524904214559387</v>
+      </c>
+      <c r="W6">
+        <v>0.1787671232876712</v>
+      </c>
+      <c r="X6">
+        <v>0.08790428741553657</v>
+      </c>
+      <c r="Y6">
+        <v>0.09086283587213465</v>
+      </c>
+      <c r="Z6">
+        <v>0.07285448632492421</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08986864206194323</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08986864206194323</v>
+      </c>
+      <c r="AD6">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AG6">
+        <v>82.82599999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.614190687361419</v>
+      </c>
+      <c r="AI6">
+        <v>0.7244986922406278</v>
+      </c>
+      <c r="AJ6">
+        <v>0.6134077881296934</v>
+      </c>
+      <c r="AK6">
+        <v>0.7238389876426686</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_financial_svcs_non_bank_insurance.xlsx
@@ -588,112 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.07919999999999999</v>
+        <v>-0.00709</v>
       </c>
       <c r="E2">
-        <v>-0.2191</v>
+        <v>0.0006499999999999995</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.05652680652680653</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.05652680652680653</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.04224941724941725</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.03583143468370291</v>
       </c>
       <c r="K2">
-        <v>5.053999999999999</v>
+        <v>5.335</v>
       </c>
       <c r="L2">
-        <v>0.4714552238805969</v>
+        <v>0.155448717948718</v>
       </c>
       <c r="M2">
-        <v>2.82</v>
+        <v>3.552</v>
       </c>
       <c r="N2">
-        <v>0.02881078872088271</v>
+        <v>0.03334272036046184</v>
       </c>
       <c r="O2">
-        <v>0.5579738820736051</v>
+        <v>0.6657919400187441</v>
       </c>
       <c r="P2">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q2">
-        <v>0.02881078872088271</v>
+        <v>0.02684689758753403</v>
       </c>
       <c r="R2">
-        <v>0.5579738820736051</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1948198198198198</v>
       </c>
       <c r="U2">
-        <v>3.397</v>
+        <v>2.35</v>
       </c>
       <c r="V2">
-        <v>0.03470576215774417</v>
+        <v>0.02205951375199474</v>
       </c>
       <c r="W2">
-        <v>0.0008904109589041096</v>
+        <v>0.02315228562491621</v>
       </c>
       <c r="X2">
-        <v>0.06636722681768881</v>
+        <v>0.0739336134195048</v>
       </c>
       <c r="Y2">
-        <v>-0.0654768158587847</v>
+        <v>-0.05078132779458859</v>
       </c>
       <c r="Z2">
-        <v>0.04562517556329216</v>
+        <v>0.1509646429545435</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07068494522063501</v>
+        <v>0.07385493511541011</v>
       </c>
       <c r="AC2">
-        <v>-0.07068494522063501</v>
+        <v>-0.06622588685240749</v>
       </c>
       <c r="AD2">
-        <v>91.87299999999999</v>
+        <v>96.684</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>91.87299999999999</v>
+        <v>96.684</v>
       </c>
       <c r="AG2">
-        <v>88.47599999999998</v>
+        <v>94.334</v>
       </c>
       <c r="AH2">
-        <v>0.4841715282498827</v>
+        <v>0.4757743068883049</v>
       </c>
       <c r="AI2">
-        <v>0.3988010747787284</v>
+        <v>0.4072894550601557</v>
       </c>
       <c r="AJ2">
-        <v>0.4747687222305694</v>
+        <v>0.4696411502310021</v>
       </c>
       <c r="AK2">
-        <v>0.3898033272240236</v>
+        <v>0.4013632070253666</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="AM2">
-        <v>-0.08599999999999999</v>
+        <v>0.633</v>
+      </c>
+      <c r="AN2">
+        <v>57.55</v>
+      </c>
+      <c r="AO2">
+        <v>1.951547779273217</v>
+      </c>
+      <c r="AP2">
+        <v>56.15119047619048</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>2.290679304897314</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dar Al Aman for Islamic Finance (ASE:DAIF)</t>
+          <t>Future Arab Investment Company (ASE:FUTR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,8 +721,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.016</v>
+      </c>
+      <c r="G3">
+        <v>0.08471615720524017</v>
+      </c>
+      <c r="H3">
+        <v>0.08471615720524017</v>
+      </c>
+      <c r="I3">
+        <v>0.06331877729257643</v>
+      </c>
+      <c r="J3">
+        <v>0.04100033439553091</v>
+      </c>
       <c r="K3">
-        <v>-0.283</v>
+        <v>0.575</v>
+      </c>
+      <c r="L3">
+        <v>0.02510917030567686</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,67 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.503</v>
+        <v>0.386</v>
       </c>
       <c r="V3">
-        <v>0.09710424710424712</v>
+        <v>0.03711538461538461</v>
       </c>
       <c r="W3">
-        <v>-0.01979020979020979</v>
+        <v>0.02068345323741007</v>
       </c>
       <c r="X3">
-        <v>0.0603979423920712</v>
+        <v>0.081532027458731</v>
       </c>
       <c r="Y3">
-        <v>-0.08018815218228099</v>
+        <v>-0.06084857422132094</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.6371376105948472</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.02612285509035829</v>
       </c>
       <c r="AB3">
-        <v>0.0603979423920712</v>
+        <v>0.08084287747892246</v>
       </c>
       <c r="AC3">
-        <v>-0.0603979423920712</v>
+        <v>-0.05472002238856417</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>7.74</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>7.74</v>
       </c>
       <c r="AG3">
-        <v>-0.503</v>
+        <v>7.354</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.4266813671444322</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.2141671278361926</v>
       </c>
       <c r="AJ3">
-        <v>-0.1075475732307034</v>
+        <v>0.4142165145882618</v>
       </c>
       <c r="AK3">
-        <v>-0.0372675409350226</v>
+        <v>0.205683280192426</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.737</v>
+      </c>
+      <c r="AN3">
+        <v>4.607142857142858</v>
+      </c>
+      <c r="AO3">
+        <v>1.951547779273217</v>
+      </c>
+      <c r="AP3">
+        <v>4.377380952380952</v>
+      </c>
+      <c r="AQ3">
+        <v>1.967435549525102</v>
       </c>
     </row>
     <row r="4">
@@ -802,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Finance Company (ASE:FFCO)</t>
+          <t>Dar Al Aman for Islamic Finance (ASE:DAIF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -810,29 +849,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.227</v>
-      </c>
-      <c r="E4">
-        <v>-0.519</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
-        <v>0.117</v>
-      </c>
-      <c r="L4">
-        <v>0.05467289719626169</v>
+        <v>-1.58</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -841,7 +859,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -850,61 +868,61 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>0.59</v>
       </c>
       <c r="V4">
-        <v>0.06538461538461539</v>
+        <v>0.09035222052067381</v>
       </c>
       <c r="W4">
-        <v>0.001780821917808219</v>
+        <v>-0.1128571428571429</v>
       </c>
       <c r="X4">
-        <v>0.0609676447606229</v>
+        <v>0.06558478095291721</v>
       </c>
       <c r="Y4">
-        <v>-0.05918682284281468</v>
+        <v>-0.1784419238100601</v>
       </c>
       <c r="Z4">
-        <v>0.03333852625019473</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06192953872454171</v>
+        <v>0.06558478095291721</v>
       </c>
       <c r="AC4">
-        <v>-0.06192953872454171</v>
+        <v>-0.06558478095291721</v>
       </c>
       <c r="AD4">
-        <v>0.9429999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9429999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.9270000000000002</v>
+        <v>-0.59</v>
       </c>
       <c r="AH4">
-        <v>0.03191957485698811</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.01443153819077789</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.03349835579807033</v>
+        <v>-0.09932659932659932</v>
       </c>
       <c r="AK4">
-        <v>-0.01460463504167126</v>
+        <v>-0.04995766299745977</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -921,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Future Arab Investment Company (ASE:FUTR)</t>
+          <t>First Finance Company (ASE:FFCO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -929,14 +947,38 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.058</v>
+      </c>
+      <c r="E5">
+        <v>0.0139</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
       <c r="K5">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="L5">
+        <v>0.4954954954954955</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02871369294605809</v>
+      </c>
+      <c r="O5">
+        <v>0.4193939393939394</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -944,59 +986,65 @@
       <c r="Q5">
         <v>-0</v>
       </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="V5">
-        <v>0.06302521008403361</v>
+        <v>0.04273858921161826</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>0.02562111801242236</v>
       </c>
       <c r="X5">
-        <v>0.07176680887475473</v>
+        <v>0.06633519938027861</v>
       </c>
       <c r="Y5">
-        <v>-0.07176680887475473</v>
+        <v>-0.04071408136785626</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.05246325209144045</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07944035171672829</v>
+        <v>0.06686699275189775</v>
       </c>
       <c r="AC5">
-        <v>-0.07944035171672829</v>
+        <v>-0.06686699275189775</v>
       </c>
       <c r="AD5">
-        <v>7.83</v>
+        <v>0.844</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>7.83</v>
+        <v>0.844</v>
       </c>
       <c r="AG5">
-        <v>7.08</v>
+        <v>-0.1860000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.3968575772934617</v>
+        <v>0.03383579217447081</v>
       </c>
       <c r="AI5">
-        <v>0.2155243600330306</v>
+        <v>0.01251408576003796</v>
       </c>
       <c r="AJ5">
-        <v>0.3730242360379347</v>
+        <v>-0.007777870703353686</v>
       </c>
       <c r="AK5">
-        <v>0.1989881956155143</v>
+        <v>-0.002800614328304275</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1022,10 +1070,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06860000000000001</v>
+        <v>-0.00709</v>
       </c>
       <c r="E6">
-        <v>0.0808</v>
+        <v>-0.0126</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1040,28 +1088,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5.22</v>
+        <v>4.69</v>
       </c>
       <c r="L6">
-        <v>0.6083916083916083</v>
+        <v>0.5797280593325094</v>
       </c>
       <c r="M6">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="N6">
-        <v>0.05402298850574712</v>
+        <v>0.04366412213740458</v>
       </c>
       <c r="O6">
-        <v>0.5402298850574713</v>
+        <v>0.6098081023454157</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q6">
-        <v>0.05402298850574712</v>
+        <v>0.04366412213740458</v>
       </c>
       <c r="R6">
-        <v>0.5402298850574713</v>
+        <v>0.6098081023454157</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1070,61 +1118,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.274</v>
+        <v>0.344</v>
       </c>
       <c r="V6">
-        <v>0.00524904214559387</v>
+        <v>0.005251908396946565</v>
       </c>
       <c r="W6">
-        <v>0.1787671232876712</v>
+        <v>0.1484177215189874</v>
       </c>
       <c r="X6">
-        <v>0.08790428741553657</v>
+        <v>0.09440602311416309</v>
       </c>
       <c r="Y6">
-        <v>0.09086283587213465</v>
+        <v>0.05401169840482427</v>
       </c>
       <c r="Z6">
-        <v>0.07285448632492421</v>
+        <v>0.07070071487249402</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08986864206194323</v>
+        <v>0.08342866258369319</v>
       </c>
       <c r="AC6">
-        <v>-0.08986864206194323</v>
+        <v>-0.08342866258369319</v>
       </c>
       <c r="AD6">
-        <v>83.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>83.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AG6">
-        <v>82.82599999999999</v>
+        <v>87.756</v>
       </c>
       <c r="AH6">
-        <v>0.614190687361419</v>
+        <v>0.5735677083333334</v>
       </c>
       <c r="AI6">
-        <v>0.7244986922406278</v>
+        <v>0.7257001647446458</v>
       </c>
       <c r="AJ6">
-        <v>0.6134077881296934</v>
+        <v>0.5726105340084564</v>
       </c>
       <c r="AK6">
-        <v>0.7238389876426686</v>
+        <v>0.7249206978588422</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.08599999999999999</v>
+        <v>-0.104</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
